--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.17409755022271</v>
+        <v>3.603290851911191</v>
       </c>
       <c r="D2" t="n">
-        <v>19.29018172830704</v>
+        <v>3.134654530849895</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8561478694334603</v>
+        <v>0.1391240287829374</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5784424887472515</v>
+        <v>0.09399690442142838</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.46180181135579</v>
+        <v>3.325042794345316</v>
       </c>
       <c r="D3" t="n">
-        <v>20.44706670580155</v>
+        <v>3.322648339692751</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8561478694334603</v>
+        <v>0.1391240287829374</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5784424887472515</v>
+        <v>0.09399690442142838</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
